--- a/testinputs/CANLinTestParameters.xlsx
+++ b/testinputs/CANLinTestParameters.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17820" activeTab="4"/>
+    <workbookView windowHeight="17820"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectInfo" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>dword</t>
   </si>
   <si>
-    <t>30513024300093</t>
+    <t>30513024300068</t>
   </si>
   <si>
     <t/>
@@ -4407,7 +4407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4419,13 +4419,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4841,7 +4839,7 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
@@ -4927,47 +4925,47 @@
       </c>
     </row>
     <row r="3" spans="1:30">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:30">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:30">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5019,123 +5017,123 @@
       </c>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:30">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:30">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:30">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:30">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:30">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:30">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5209,7 +5207,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AD22 A23:B24 D23:AD24" numberStoredAsText="1"/>
+    <ignoredError sqref="D23:AD24 A23:B24 A1:AD1 A2:B2 D2:AD2 A3:AD22" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5586,7 +5584,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A3:C15 A1:C1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A3:C15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7517,397 +7515,397 @@
   <dimension ref="A1:Y5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="6" width="9" style="5"/>
-    <col min="7" max="7" width="15.5" style="5" customWidth="1"/>
-    <col min="8" max="9" width="9" style="5"/>
-    <col min="10" max="10" width="10.6" style="5" customWidth="1"/>
-    <col min="11" max="21" width="9" style="5"/>
-    <col min="22" max="22" width="15" style="5" customWidth="1"/>
-    <col min="23" max="23" width="70.7" style="5" customWidth="1"/>
-    <col min="24" max="24" width="57.4" style="5" customWidth="1"/>
-    <col min="25" max="25" width="46.2" style="5" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="5"/>
+    <col min="1" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="10.6" style="1" customWidth="1"/>
+    <col min="11" max="21" width="9" style="1"/>
+    <col min="22" max="22" width="15" style="1" customWidth="1"/>
+    <col min="23" max="23" width="70.7" style="1" customWidth="1"/>
+    <col min="24" max="24" width="57.4" style="1" customWidth="1"/>
+    <col min="25" max="25" width="46.2" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="V2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="5">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="V3" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="5">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="V4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>1</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>3</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M5" s="6">
-        <v>8</v>
-      </c>
-      <c r="N5" s="5" t="s">
+      <c r="M5" s="5">
+        <v>8</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="5">
         <v>100</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="5">
         <v>1</v>
       </c>
-      <c r="R5" s="6">
+      <c r="R5" s="5">
         <v>300</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="5">
         <v>2</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="5">
         <v>1</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="5">
         <v>1</v>
       </c>
-      <c r="V5" s="6">
+      <c r="V5" s="5">
         <v>3</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="1" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7915,7 +7913,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B2:Y3 B4:G4 A1:Y1 I4:Y4" numberStoredAsText="1"/>
+    <ignoredError sqref="I4:Y4 A1:Y1 B4:G4 B2:Y3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11802,7 +11800,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B5 D1:F5" numberStoredAsText="1"/>
+    <ignoredError sqref="D1:F5 A1:B5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13576,7 +13574,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E48 A49:B49 D49:E49 A50:E50" numberStoredAsText="1"/>
+    <ignoredError sqref="A50:E50 D49:E49 A49:B49 A1:E48" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14615,7 +14613,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A16:G50 A1:G13 B14:G15" numberStoredAsText="1"/>
+    <ignoredError sqref="B14:G15 A1:G13 A16:G50" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14737,7 +14735,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:M2 B3:D3 F3:J3 M3 A4:M13" numberStoredAsText="1"/>
+    <ignoredError sqref="A4:M13 M3 F3:J3 B3:D3 A1:M2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14792,7 +14790,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 C2:E2" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:E2 A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
